--- a/Kr-Ar Separation/analysis/2026_08_recovery_for_different_amounts/volume_v_recovery.xlsx
+++ b/Kr-Ar Separation/analysis/2026_08_recovery_for_different_amounts/volume_v_recovery.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fatmayakut/Desktop/Physik/MA/Kr:Ar Separation/analysis/2026_08_recovery_for_different_amounts/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fatmayakut/Desktop/Physik/MA/Kr-Ar Separation/analysis/2026_08_recovery_for_different_amounts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1234CF32-EC24-AA44-AE25-B45546141AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0256833C-EBD3-3D41-B98C-14078F7CC120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="600" windowWidth="23260" windowHeight="17400" xr2:uid="{8B558523-AAC9-124C-AA38-7CB1369EC6B4}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{8B558523-AAC9-124C-AA38-7CB1369EC6B4}"/>
   </bookViews>
   <sheets>
     <sheet name="volume_v_recovery" sheetId="1" r:id="rId1"/>
+    <sheet name="volume_v_recovery_adjusted" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
   <si>
     <t>Recovery</t>
   </si>
@@ -48,6 +49,135 @@
   </si>
   <si>
     <t>Output</t>
+  </si>
+  <si>
+    <t>H2 Ratio</t>
+  </si>
+  <si>
+    <t>H2 Ratio/7</t>
+  </si>
+  <si>
+    <t>Output Kr</t>
+  </si>
+  <si>
+    <t>Input Kr</t>
+  </si>
+  <si>
+    <t>Replica 1</t>
+  </si>
+  <si>
+    <t>Replica 2</t>
+  </si>
+  <si>
+    <t>Replica 3</t>
+  </si>
+  <si>
+    <t>Replica 10</t>
+  </si>
+  <si>
+    <t>Replica 9</t>
+  </si>
+  <si>
+    <t>Replica 4</t>
+  </si>
+  <si>
+    <t>Replica 5</t>
+  </si>
+  <si>
+    <t>Replica 6</t>
+  </si>
+  <si>
+    <t>Replica 7</t>
+  </si>
+  <si>
+    <t>Replica 8</t>
+  </si>
+  <si>
+    <t>Output + 6/7*H2</t>
+  </si>
+  <si>
+    <t>Total Gas Out</t>
+  </si>
+  <si>
+    <t>Kr in</t>
+  </si>
+  <si>
+    <t>1/7 H2 in</t>
+  </si>
+  <si>
+    <t>1/7 H2 out</t>
+  </si>
+  <si>
+    <t>Kr out</t>
+  </si>
+  <si>
+    <t>Total out</t>
+  </si>
+  <si>
+    <t>Total in</t>
+  </si>
+  <si>
+    <t>H2 ratio out</t>
+  </si>
+  <si>
+    <t>H2 ratio in</t>
+  </si>
+  <si>
+    <t>Kr out 2</t>
+  </si>
+  <si>
+    <t>Kr in 2</t>
+  </si>
+  <si>
+    <t>Kr in ratio</t>
+  </si>
+  <si>
+    <t>Kr out ratio</t>
+  </si>
+  <si>
+    <t>p1</t>
+  </si>
+  <si>
+    <t>Kr1 [%]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2_1 [%] </t>
+  </si>
+  <si>
+    <t>p2</t>
+  </si>
+  <si>
+    <t>Kr2 [%]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2_2 [%] </t>
+  </si>
+  <si>
+    <t>total in</t>
+  </si>
+  <si>
+    <t>total out</t>
+  </si>
+  <si>
+    <t>recovery</t>
+  </si>
+  <si>
+    <t>difference</t>
+  </si>
+  <si>
+    <t>p1_</t>
+  </si>
+  <si>
+    <t>p2_</t>
+  </si>
+  <si>
+    <t>Kr_ out</t>
+  </si>
+  <si>
+    <t>recovery_</t>
+  </si>
+  <si>
+    <t>Kr_ in</t>
   </si>
 </sst>
 </file>
@@ -57,7 +187,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -72,13 +202,49 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FFA4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE400"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -94,9 +260,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -104,6 +278,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFF3FFA4"/>
+      <color rgb="FFFFE400"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -447,30 +627,34 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="B2" s="1"/>
+      <c r="A2">
+        <v>0.51</v>
+      </c>
+      <c r="B2">
+        <v>0.46</v>
+      </c>
       <c r="C2">
         <f t="shared" ref="C2:C3" si="0">B2/A2</f>
-        <v>0</v>
+        <v>0.90196078431372551</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1"/>
+      <c r="A3">
+        <v>0.9</v>
+      </c>
+      <c r="B3">
+        <v>13.01</v>
+      </c>
       <c r="C3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14.455555555555556</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>2.77</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
         <v>1.81</v>
       </c>
       <c r="C4">
@@ -479,85 +663,1876 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>5</v>
+      <c r="A5">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="B5">
+        <v>3.47</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C12" si="1">B5/A5</f>
-        <v>0</v>
+        <v>0.73361522198731499</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>5</v>
+      <c r="A6">
+        <v>5.51</v>
+      </c>
+      <c r="B6">
+        <v>3.42</v>
       </c>
       <c r="C6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.62068965517241381</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1"/>
+      <c r="A7">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="B7">
+        <v>13.54</v>
+      </c>
       <c r="C7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.5563218390804598</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>10</v>
-      </c>
-      <c r="B8" s="1"/>
+      <c r="A8">
+        <v>9.11</v>
+      </c>
+      <c r="B8">
+        <v>5.22</v>
+      </c>
       <c r="C8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.57299670691547755</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1"/>
+      <c r="A9">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="B9">
+        <v>9.14</v>
+      </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.9251012145748988</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>20</v>
-      </c>
-      <c r="B10" s="1"/>
+      <c r="A10">
+        <v>15.8</v>
+      </c>
+      <c r="B10">
+        <v>15.63</v>
+      </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.98924050632911398</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1"/>
+      <c r="A11">
+        <v>20.21</v>
+      </c>
+      <c r="B11">
+        <v>18.55</v>
+      </c>
       <c r="C11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.91786244433448783</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>25</v>
-      </c>
-      <c r="B12" s="1"/>
+      <c r="A12">
+        <v>22.11</v>
+      </c>
+      <c r="B12">
+        <v>21.4</v>
+      </c>
       <c r="C12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.96788783355947527</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB47AB1A-2BFC-674F-8971-6B4457BC2F49}">
+  <dimension ref="A1:V50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>0.48</v>
+      </c>
+      <c r="C2">
+        <v>0.46</v>
+      </c>
+      <c r="D2">
+        <v>0.48899999999999999</v>
+      </c>
+      <c r="E2">
+        <f>D2/7</f>
+        <v>6.9857142857142854E-2</v>
+      </c>
+      <c r="F2">
+        <v>1.79</v>
+      </c>
+      <c r="G2">
+        <f>C2+(D2-E2)*F2</f>
+        <v>1.2102657142857143</v>
+      </c>
+      <c r="H2">
+        <f>G2/B2</f>
+        <v>2.5213869047619046</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>1.01</v>
+      </c>
+      <c r="C3">
+        <v>13.01</v>
+      </c>
+      <c r="D3">
+        <v>0.219</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E12" si="0">D3/7</f>
+        <v>3.1285714285714285E-2</v>
+      </c>
+      <c r="F3">
+        <v>20.48</v>
+      </c>
+      <c r="G3">
+        <f>C3+(D3-E3)*F3</f>
+        <v>16.854388571428572</v>
+      </c>
+      <c r="H3">
+        <f>G3/B3</f>
+        <v>16.687513437057991</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>2.77</v>
+      </c>
+      <c r="C4">
+        <v>1.79</v>
+      </c>
+      <c r="D4">
+        <v>0.29599999999999999</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>4.2285714285714281E-2</v>
+      </c>
+      <c r="F4">
+        <v>3.5</v>
+      </c>
+      <c r="G4">
+        <f>C4+(D4-E4)*F4</f>
+        <v>2.6779999999999999</v>
+      </c>
+      <c r="H4">
+        <f>G4/B4</f>
+        <v>0.96678700361010828</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="C5">
+        <v>3.44</v>
+      </c>
+      <c r="D5">
+        <v>0.156</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>2.2285714285714287E-2</v>
+      </c>
+      <c r="F5">
+        <v>5.3460000000000001</v>
+      </c>
+      <c r="G5">
+        <f>C5+(D5-E5)*F5</f>
+        <v>4.1548365714285715</v>
+      </c>
+      <c r="H5">
+        <f>G5/B5</f>
+        <v>0.87840096647538501</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>5.53</v>
+      </c>
+      <c r="C6">
+        <v>3.39</v>
+      </c>
+      <c r="D6">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>3.9714285714285716E-2</v>
+      </c>
+      <c r="F6">
+        <v>6.15</v>
+      </c>
+      <c r="G6">
+        <f>C6+(D6-E6)*F6</f>
+        <v>4.8554571428571434</v>
+      </c>
+      <c r="H6">
+        <f>G6/B6</f>
+        <v>0.87802118315680711</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>8.67</v>
+      </c>
+      <c r="C7">
+        <v>13.54</v>
+      </c>
+      <c r="D7">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>4.8571428571428576E-3</v>
+      </c>
+      <c r="F7">
+        <v>18.93</v>
+      </c>
+      <c r="G7">
+        <f>C7+(D7-E7)*F7</f>
+        <v>14.091674285714285</v>
+      </c>
+      <c r="H7">
+        <f>G7/B7</f>
+        <v>1.625337287856319</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8">
+        <v>9.11</v>
+      </c>
+      <c r="C8">
+        <v>5.22</v>
+      </c>
+      <c r="D8">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>1.3857142857142858E-2</v>
+      </c>
+      <c r="F8">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="G8">
+        <f>C8+(D8-E8)*F8</f>
+        <v>5.9308714285714288</v>
+      </c>
+      <c r="H8">
+        <f>G8/B8</f>
+        <v>0.65102869687941045</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="C9">
+        <v>9.14</v>
+      </c>
+      <c r="D9">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>1.0714285714285714E-2</v>
+      </c>
+      <c r="F9">
+        <v>11.43</v>
+      </c>
+      <c r="G9">
+        <f>C9+(D9-E9)*F9</f>
+        <v>9.8747857142857143</v>
+      </c>
+      <c r="H9">
+        <f>G9/B9</f>
+        <v>0.99947223828802767</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>15.84</v>
+      </c>
+      <c r="C10">
+        <v>15.93</v>
+      </c>
+      <c r="D10">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F10">
+        <v>21.85</v>
+      </c>
+      <c r="G10">
+        <f>C10+(D10-E10)*F10</f>
+        <v>16.9788</v>
+      </c>
+      <c r="H10">
+        <f>G10/B10</f>
+        <v>1.0718939393939393</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>20.13</v>
+      </c>
+      <c r="C11">
+        <v>18.510000000000002</v>
+      </c>
+      <c r="D11">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>7.2857142857142851E-3</v>
+      </c>
+      <c r="F11">
+        <v>22.6</v>
+      </c>
+      <c r="G11">
+        <f>C11+(D11-E11)*F11</f>
+        <v>19.49794285714286</v>
+      </c>
+      <c r="H11">
+        <f>G11/B11</f>
+        <v>0.96860123483074323</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>22.11</v>
+      </c>
+      <c r="C12">
+        <v>21.43</v>
+      </c>
+      <c r="D12">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="F12">
+        <v>25.64</v>
+      </c>
+      <c r="G12">
+        <f>C12+(D12-E12)*F12</f>
+        <v>22.35304</v>
+      </c>
+      <c r="H12">
+        <f>G12/B12</f>
+        <v>1.0109923111714156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17">
+        <v>1.64</v>
+      </c>
+      <c r="C17">
+        <v>0.48</v>
+      </c>
+      <c r="D17">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="E17">
+        <v>1.79</v>
+      </c>
+      <c r="F17">
+        <v>0.46</v>
+      </c>
+      <c r="G17">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="H17">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="I17">
+        <f>H17/7</f>
+        <v>7.6428571428571429E-2</v>
+      </c>
+      <c r="J17">
+        <v>0.48899999999999999</v>
+      </c>
+      <c r="K17">
+        <f>J17/7</f>
+        <v>6.9857142857142854E-2</v>
+      </c>
+      <c r="L17">
+        <f>C17+D17*(H17-I17)*B17</f>
+        <v>0.70185685714285717</v>
+      </c>
+      <c r="M17">
+        <f>F17+G17*(J17-K17)*E17</f>
+        <v>0.65356855428571436</v>
+      </c>
+      <c r="N17">
+        <f>M17/L17</f>
+        <v>0.93119921481751067</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <v>16.54</v>
+      </c>
+      <c r="C18">
+        <v>1.01</v>
+      </c>
+      <c r="D18">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="E18">
+        <v>20.48</v>
+      </c>
+      <c r="F18">
+        <v>13.01</v>
+      </c>
+      <c r="G18">
+        <v>0.64</v>
+      </c>
+      <c r="H18">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="I18">
+        <f t="shared" ref="I18:I27" si="1">H18/7</f>
+        <v>6.3428571428571431E-2</v>
+      </c>
+      <c r="J18">
+        <v>0.219</v>
+      </c>
+      <c r="K18">
+        <f t="shared" ref="K18:K27" si="2">J18/7</f>
+        <v>3.1285714285714285E-2</v>
+      </c>
+      <c r="L18">
+        <f t="shared" ref="L18:L27" si="3">C18+D18*(H18-I18)*B18</f>
+        <v>1.9416084114285712</v>
+      </c>
+      <c r="M18">
+        <f t="shared" ref="M18:M28" si="4">F18+G18*(J18-K18)*E18</f>
+        <v>15.470408685714286</v>
+      </c>
+      <c r="N18">
+        <f t="shared" ref="N18:N27" si="5">M18/L18</f>
+        <v>7.9678315126023129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19">
+        <v>3.69</v>
+      </c>
+      <c r="C19">
+        <v>2.77</v>
+      </c>
+      <c r="D19">
+        <v>0.752</v>
+      </c>
+      <c r="E19">
+        <v>3.5</v>
+      </c>
+      <c r="F19">
+        <v>1.79</v>
+      </c>
+      <c r="G19">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="H19">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="1"/>
+        <v>2.3142857142857142E-2</v>
+      </c>
+      <c r="J19">
+        <v>0.29599999999999999</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="2"/>
+        <v>4.2285714285714281E-2</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="3"/>
+        <v>3.1553119085714285</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="4"/>
+        <v>2.2437680000000002</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="5"/>
+        <v>0.71110814557026436</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20">
+        <v>6.11</v>
+      </c>
+      <c r="C20">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="D20">
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="E20">
+        <v>5.3460000000000001</v>
+      </c>
+      <c r="F20">
+        <v>3.44</v>
+      </c>
+      <c r="G20">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="H20">
+        <v>0.152</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="1"/>
+        <v>2.1714285714285714E-2</v>
+      </c>
+      <c r="J20">
+        <v>0.156</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="2"/>
+        <v>2.2285714285714287E-2</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="3"/>
+        <v>5.3461393828571433</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="4"/>
+        <v>3.8996399154285712</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="5"/>
+        <v>0.72943102230613421</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>6.72</v>
+      </c>
+      <c r="C21">
+        <v>5.53</v>
+      </c>
+      <c r="D21">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="E21">
+        <v>6.15</v>
+      </c>
+      <c r="F21">
+        <v>3.39</v>
+      </c>
+      <c r="G21">
+        <v>0.55200000000000005</v>
+      </c>
+      <c r="H21">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="1"/>
+        <v>1.942857142857143E-2</v>
+      </c>
+      <c r="J21">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="2"/>
+        <v>3.9714285714285716E-2</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="3"/>
+        <v>6.1754886400000002</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="4"/>
+        <v>4.1989323428571428</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="5"/>
+        <v>0.67993523875337303</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22">
+        <v>21.1</v>
+      </c>
+      <c r="C22">
+        <v>8.67</v>
+      </c>
+      <c r="D22">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="E22">
+        <v>18.93</v>
+      </c>
+      <c r="F22">
+        <v>13.54</v>
+      </c>
+      <c r="G22">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="H22">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="1"/>
+        <v>4.928571428571428E-2</v>
+      </c>
+      <c r="J22">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="2"/>
+        <v>4.8571428571428576E-3</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="3"/>
+        <v>11.234463857142856</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="4"/>
+        <v>13.934447114285714</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="5"/>
+        <v>1.2403304057475082</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23">
+        <v>11.8</v>
+      </c>
+      <c r="C23">
+        <v>9.11</v>
+      </c>
+      <c r="D23">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="E23">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="F23">
+        <v>5.22</v>
+      </c>
+      <c r="G23">
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="H23">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="1"/>
+        <v>1.6999999999999998E-2</v>
+      </c>
+      <c r="J23">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="2"/>
+        <v>1.3857142857142858E-2</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="3"/>
+        <v>10.0391792</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="4"/>
+        <v>5.6543424428571427</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="5"/>
+        <v>0.56322756374915017</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24">
+        <v>11.99</v>
+      </c>
+      <c r="C24">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="D24">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="E24">
+        <v>11.43</v>
+      </c>
+      <c r="F24">
+        <v>9.14</v>
+      </c>
+      <c r="G24">
+        <v>0.79900000000000004</v>
+      </c>
+      <c r="H24">
+        <v>0.112</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="1"/>
+        <v>1.6E-2</v>
+      </c>
+      <c r="J24">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="2"/>
+        <v>1.0714285714285714E-2</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="3"/>
+        <v>10.82845696</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="4"/>
+        <v>9.7270937857142865</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="5"/>
+        <v>0.89828992456135559</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25">
+        <v>30.65</v>
+      </c>
+      <c r="C25">
+        <v>15.84</v>
+      </c>
+      <c r="D25">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="E25">
+        <v>21.85</v>
+      </c>
+      <c r="F25">
+        <v>15.93</v>
+      </c>
+      <c r="G25">
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="H25">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="1"/>
+        <v>4.9714285714285711E-2</v>
+      </c>
+      <c r="J25">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="2"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="3"/>
+        <v>20.566650342857145</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="4"/>
+        <v>16.694575199999999</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="5"/>
+        <v>0.81173039467742358</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26">
+        <v>31.8</v>
+      </c>
+      <c r="C26">
+        <v>20.13</v>
+      </c>
+      <c r="D26">
+        <v>0.63300000000000001</v>
+      </c>
+      <c r="E26">
+        <v>22.6</v>
+      </c>
+      <c r="F26">
+        <v>18.510000000000002</v>
+      </c>
+      <c r="G26">
+        <v>0.81899999999999995</v>
+      </c>
+      <c r="H26">
+        <v>3.9E-2</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="1"/>
+        <v>5.5714285714285718E-3</v>
+      </c>
+      <c r="J26">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="2"/>
+        <v>7.2857142857142851E-3</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="3"/>
+        <v>20.802897085714285</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="4"/>
+        <v>19.319125200000002</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="5"/>
+        <v>0.92867474757959478</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27">
+        <v>27.43</v>
+      </c>
+      <c r="C27">
+        <v>22.53</v>
+      </c>
+      <c r="D27">
+        <v>0.82099999999999995</v>
+      </c>
+      <c r="E27">
+        <v>25.64</v>
+      </c>
+      <c r="F27">
+        <v>21.43</v>
+      </c>
+      <c r="G27">
+        <v>0.83599999999999997</v>
+      </c>
+      <c r="H27">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="1"/>
+        <v>6.8571428571428577E-3</v>
+      </c>
+      <c r="J27">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="2"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="3"/>
+        <v>23.456538377142859</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="4"/>
+        <v>22.201661439999999</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="5"/>
+        <v>0.9465020406265201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B33" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N33" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="R33" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="U33" t="s">
+        <v>39</v>
+      </c>
+      <c r="V33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="C34">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="D34">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="E34">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="F34">
+        <f>(B34-C34)*D34*41.25</f>
+        <v>0.48431625</v>
+      </c>
+      <c r="G34">
+        <f>(B34-C34)*41.25</f>
+        <v>1.64175</v>
+      </c>
+      <c r="H34">
+        <f>F34+G34*6/7*E34*D34</f>
+        <v>0.70640984464285717</v>
+      </c>
+      <c r="I34">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="J34">
+        <v>1.5E-3</v>
+      </c>
+      <c r="K34">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="L34">
+        <v>0.48899999999999999</v>
+      </c>
+      <c r="M34">
+        <f>(I34-J34)*K34*41.25</f>
+        <v>0.46294875000000002</v>
+      </c>
+      <c r="N34">
+        <f>(I34-J34)*41.25</f>
+        <v>1.7943749999999998</v>
+      </c>
+      <c r="O34">
+        <f>M34+N34*6/7*L34*K34</f>
+        <v>0.65699041178571427</v>
+      </c>
+      <c r="P34">
+        <f>M34/F34</f>
+        <v>0.95588110041734098</v>
+      </c>
+      <c r="Q34">
+        <f>O34/H34</f>
+        <v>0.93004141543054497</v>
+      </c>
+      <c r="R34">
+        <f>Q34-P34</f>
+        <v>-2.5839684986796008E-2</v>
+      </c>
+      <c r="U34">
+        <v>0.95588110041734098</v>
+      </c>
+      <c r="V34">
+        <v>0.93004141543054497</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="F35" s="4">
+        <f>(B35-C35)*D35*17.09</f>
+        <v>1.014004388</v>
+      </c>
+      <c r="G35" s="4">
+        <f>(B35-C35)*17.09</f>
+        <v>6.8513810000000008</v>
+      </c>
+      <c r="H35" s="3">
+        <f>F35+G35*6/7*E35*D35</f>
+        <v>1.3999054865188572</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0.4965</v>
+      </c>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3">
+        <v>0.64</v>
+      </c>
+      <c r="L35" s="3">
+        <v>0.219</v>
+      </c>
+      <c r="M35" s="3">
+        <f t="shared" ref="M35:M44" si="6">(I35-J35)*K35*41.25</f>
+        <v>13.1076</v>
+      </c>
+      <c r="N35" s="3">
+        <f>(I35-J35)*41.25</f>
+        <v>20.480625</v>
+      </c>
+      <c r="O35" s="3">
+        <f>M35+N35*6/7*L35*K35</f>
+        <v>15.56808377142857</v>
+      </c>
+      <c r="P35" s="3">
+        <f>M35/F35</f>
+        <v>12.926571280281284</v>
+      </c>
+      <c r="Q35" s="3">
+        <f>O35/H35</f>
+        <v>11.120810598536691</v>
+      </c>
+      <c r="R35" s="3">
+        <f t="shared" ref="R35:R44" si="7">Q35-P35</f>
+        <v>-1.8057606817445926</v>
+      </c>
+      <c r="U35">
+        <v>12.926571280281284</v>
+      </c>
+      <c r="V35">
+        <v>11.120810598536691</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="C36">
+        <v>1.5E-3</v>
+      </c>
+      <c r="D36">
+        <v>0.752</v>
+      </c>
+      <c r="E36">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="F36">
+        <f t="shared" ref="F35:F44" si="8">(B36-C36)*D36*41.25</f>
+        <v>2.7762899999999999</v>
+      </c>
+      <c r="G36">
+        <f t="shared" ref="G35:G44" si="9">(B36-C36)*41.25</f>
+        <v>3.691875</v>
+      </c>
+      <c r="H36">
+        <f t="shared" ref="H35:H59" si="10">F36+G36*6/7*E36*D36</f>
+        <v>3.1617976971428572</v>
+      </c>
+      <c r="I36">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="J36">
+        <v>1E-3</v>
+      </c>
+      <c r="K36">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="L36">
+        <v>0.29599999999999999</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="6"/>
+        <v>1.7916937499999999</v>
+      </c>
+      <c r="N36">
+        <f t="shared" ref="N35:N44" si="11">(I36-J36)*41.25</f>
+        <v>3.5062499999999996</v>
+      </c>
+      <c r="O36">
+        <f>M36+N36*6/7*L36*K36</f>
+        <v>2.24627205</v>
+      </c>
+      <c r="P36">
+        <f>M36/F36</f>
+        <v>0.64535540235350053</v>
+      </c>
+      <c r="Q36">
+        <f>O36/H36</f>
+        <v>0.71044142135653798</v>
+      </c>
+      <c r="R36">
+        <f t="shared" si="7"/>
+        <v>6.5086019003037454E-2</v>
+      </c>
+      <c r="U36">
+        <v>0.64535540235350053</v>
+      </c>
+      <c r="V36">
+        <v>0.71044142135653798</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37">
+        <v>0.14949999999999999</v>
+      </c>
+      <c r="C37">
+        <v>1.5E-3</v>
+      </c>
+      <c r="D37">
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="E37">
+        <v>0.152</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="8"/>
+        <v>4.7252700000000001</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="9"/>
+        <v>6.1049999999999995</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="10"/>
+        <v>5.3409051771428571</v>
+      </c>
+      <c r="I37">
+        <v>0.1308</v>
+      </c>
+      <c r="J37">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="K37">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="L37">
+        <v>0.156</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="6"/>
+        <v>3.437478</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="11"/>
+        <v>5.3460000000000001</v>
+      </c>
+      <c r="O37">
+        <f>M37+N37*6/7*L37*K37</f>
+        <v>3.8971179154285713</v>
+      </c>
+      <c r="P37">
+        <f>M37/F37</f>
+        <v>0.72746700188560653</v>
+      </c>
+      <c r="Q37">
+        <f>O37/H37</f>
+        <v>0.72967367630993096</v>
+      </c>
+      <c r="R37">
+        <f t="shared" si="7"/>
+        <v>2.2066744243244285E-3</v>
+      </c>
+      <c r="U37">
+        <v>0.72746700188560653</v>
+      </c>
+      <c r="V37">
+        <v>0.72967367630993096</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38">
+        <v>0.1643</v>
+      </c>
+      <c r="C38">
+        <v>1.5E-3</v>
+      </c>
+      <c r="D38">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="E38">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="8"/>
+        <v>5.5335719999999995</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="9"/>
+        <v>6.7154999999999996</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="10"/>
+        <v>6.1786283931428567</v>
+      </c>
+      <c r="I38">
+        <v>0.15</v>
+      </c>
+      <c r="J38">
+        <v>1E-3</v>
+      </c>
+      <c r="K38">
+        <v>0.55200000000000005</v>
+      </c>
+      <c r="L38">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="M38" s="2">
+        <f t="shared" si="6"/>
+        <v>3.3927300000000002</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="11"/>
+        <v>6.1462499999999993</v>
+      </c>
+      <c r="O38">
+        <f>M38+N38*6/7*L38*K38</f>
+        <v>4.2011690914285715</v>
+      </c>
+      <c r="P38">
+        <f>M38/F38</f>
+        <v>0.6131175305932588</v>
+      </c>
+      <c r="Q38">
+        <f>O38/H38</f>
+        <v>0.67995173428638267</v>
+      </c>
+      <c r="R38">
+        <f t="shared" si="7"/>
+        <v>6.6834203693123873E-2</v>
+      </c>
+      <c r="U38">
+        <v>0.6131175305932588</v>
+      </c>
+      <c r="V38">
+        <v>0.67995173428638267</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39">
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="D39">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="E39">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="F39" s="2">
+        <f t="shared" si="8"/>
+        <v>8.6972737500000008</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="9"/>
+        <v>21.161249999999999</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="10"/>
+        <v>11.269181844642858</v>
+      </c>
+      <c r="I39">
+        <v>0.46050000000000002</v>
+      </c>
+      <c r="J39">
+        <v>1.5E-3</v>
+      </c>
+      <c r="K39">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="L39">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="6"/>
+        <v>13.53763125</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="11"/>
+        <v>18.93375</v>
+      </c>
+      <c r="O39">
+        <f>M39+N39*6/7*L39*K39</f>
+        <v>13.932156503571429</v>
+      </c>
+      <c r="P39">
+        <f>M39/F39</f>
+        <v>1.556537328723268</v>
+      </c>
+      <c r="Q39">
+        <f>O39/H39</f>
+        <v>1.2363059444456914</v>
+      </c>
+      <c r="R39">
+        <f t="shared" si="7"/>
+        <v>-0.32023138427757658</v>
+      </c>
+      <c r="U39">
+        <v>1.556537328723268</v>
+      </c>
+      <c r="V39">
+        <v>1.2363059444456914</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="C40">
+        <v>2E-3</v>
+      </c>
+      <c r="D40">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="E40">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="8"/>
+        <v>9.1076699999999988</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="9"/>
+        <v>11.797499999999999</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="10"/>
+        <v>10.036652339999998</v>
+      </c>
+      <c r="I40">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="J40">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="K40">
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="L40">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="6"/>
+        <v>5.2247373749999992</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="11"/>
+        <v>8.551124999999999</v>
+      </c>
+      <c r="O40">
+        <f>M40+N40*6/7*L40*K40</f>
+        <v>5.6591369681785704</v>
+      </c>
+      <c r="P40">
+        <f>M40/F40</f>
+        <v>0.57366344795101276</v>
+      </c>
+      <c r="Q40">
+        <f>O40/H40</f>
+        <v>0.5638470653830151</v>
+      </c>
+      <c r="R40">
+        <f t="shared" si="7"/>
+        <v>-9.8163825679976613E-3</v>
+      </c>
+      <c r="U40">
+        <v>0.57366344795101276</v>
+      </c>
+      <c r="V40" s="8">
+        <v>0.5638470653830151</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="C41">
+        <v>2.3E-3</v>
+      </c>
+      <c r="D41">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="E41">
+        <v>0.112</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="8"/>
+        <v>9.8808929999999986</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="9"/>
+        <v>11.991374999999998</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="10"/>
+        <v>10.829458727999999</v>
+      </c>
+      <c r="I41">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="J41">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="K41">
+        <v>0.79900000000000004</v>
+      </c>
+      <c r="L41">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="6"/>
+        <v>9.1394613750000016</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="11"/>
+        <v>11.438625000000002</v>
+      </c>
+      <c r="O41">
+        <f>M41+N41*6/7*L41*K41</f>
+        <v>9.7269981776785723</v>
+      </c>
+      <c r="P41">
+        <f>M41/F41</f>
+        <v>0.92496309544086786</v>
+      </c>
+      <c r="Q41">
+        <f>O41/H41</f>
+        <v>0.8981980006562128</v>
+      </c>
+      <c r="R41">
+        <f t="shared" si="7"/>
+        <v>-2.6765094784655052E-2</v>
+      </c>
+      <c r="U41">
+        <v>0.92496309544086786</v>
+      </c>
+      <c r="V41" s="7">
+        <v>0.8981980006562128</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A42" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42">
+        <v>0.749</v>
+      </c>
+      <c r="C42">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="D42">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="E42">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="8"/>
+        <v>15.845403749999999</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="9"/>
+        <v>30.64875</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="10"/>
+        <v>20.571861325714284</v>
+      </c>
+      <c r="I42">
+        <v>0.53090000000000004</v>
+      </c>
+      <c r="J42">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="K42">
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="L42">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="6"/>
+        <v>15.93174825</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="11"/>
+        <v>21.85425</v>
+      </c>
+      <c r="O42">
+        <f>M42+N42*6/7*L42*K42</f>
+        <v>16.696472166</v>
+      </c>
+      <c r="P42">
+        <f>M42/F42</f>
+        <v>1.0054491827006933</v>
+      </c>
+      <c r="Q42">
+        <f>O42/H42</f>
+        <v>0.81161698990892228</v>
+      </c>
+      <c r="R42">
+        <f t="shared" si="7"/>
+        <v>-0.193832192791771</v>
+      </c>
+      <c r="U42">
+        <v>1.0054491827006933</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0.81161698990892228</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43">
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="C43">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D43">
+        <v>0.63300000000000001</v>
+      </c>
+      <c r="E43">
+        <v>3.9E-2</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="8"/>
+        <v>20.131773750000001</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="9"/>
+        <v>31.803750000000001</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="10"/>
+        <v>20.804750186785714</v>
+      </c>
+      <c r="I43">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="J43">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="K43">
+        <v>0.81899999999999995</v>
+      </c>
+      <c r="L43">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="6"/>
+        <v>18.506738250000001</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="11"/>
+        <v>22.596750000000004</v>
+      </c>
+      <c r="O43">
+        <f>M43+N43*6/7*L43*K43</f>
+        <v>19.315747093500001</v>
+      </c>
+      <c r="P43">
+        <f>M43/F43</f>
+        <v>0.91928006343703328</v>
+      </c>
+      <c r="Q43">
+        <f>O43/H43</f>
+        <v>0.92842965765426666</v>
+      </c>
+      <c r="R43">
+        <f t="shared" si="7"/>
+        <v>9.1495942172333811E-3</v>
+      </c>
+      <c r="U43">
+        <v>0.91928006343703328</v>
+      </c>
+      <c r="V43">
+        <v>0.92842965765426666</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44">
+        <v>0.67</v>
+      </c>
+      <c r="C44">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="D44">
+        <v>0.82099999999999995</v>
+      </c>
+      <c r="E44">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="8"/>
+        <v>22.527829499999999</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="9"/>
+        <v>27.439499999999999</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="10"/>
+        <v>23.454688770857143</v>
+      </c>
+      <c r="I44">
+        <v>0.62270000000000003</v>
+      </c>
+      <c r="J44">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="K44">
+        <v>0.83599999999999997</v>
+      </c>
+      <c r="L44">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="6"/>
+        <v>21.432427499999999</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="11"/>
+        <v>25.636875000000003</v>
+      </c>
+      <c r="O44">
+        <f>M44+N44*6/7*L44*K44</f>
+        <v>22.203994890000001</v>
+      </c>
+      <c r="P44">
+        <f>M44/F44</f>
+        <v>0.95137560855563119</v>
+      </c>
+      <c r="Q44">
+        <f>O44/H44</f>
+        <v>0.94667616811819943</v>
+      </c>
+      <c r="R44">
+        <f t="shared" si="7"/>
+        <v>-4.6994404374317567E-3</v>
+      </c>
+      <c r="U44">
+        <v>0.95137560855563119</v>
+      </c>
+      <c r="V44" s="8">
+        <v>0.94667616811819943</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="O20">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="formula" val="MOD(ROW(),2)=0"/>
+        <cfvo type="max"/>
+        <color theme="0" tint="-0.14999847407452621"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Kr-Ar Separation/analysis/2026_08_recovery_for_different_amounts/volume_v_recovery.xlsx
+++ b/Kr-Ar Separation/analysis/2026_08_recovery_for_different_amounts/volume_v_recovery.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fatmayakut/Desktop/Physik/MA/Kr-Ar Separation/analysis/2026_08_recovery_for_different_amounts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0256833C-EBD3-3D41-B98C-14078F7CC120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0D8060-DB6E-1849-98FF-660A5AFCF403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{8B558523-AAC9-124C-AA38-7CB1369EC6B4}"/>
+    <workbookView xWindow="980" yWindow="600" windowWidth="23280" windowHeight="17400" activeTab="1" xr2:uid="{8B558523-AAC9-124C-AA38-7CB1369EC6B4}"/>
   </bookViews>
   <sheets>
     <sheet name="volume_v_recovery" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="48">
   <si>
     <t>Recovery</t>
   </si>
@@ -159,12 +159,6 @@
     <t>total out</t>
   </si>
   <si>
-    <t>recovery</t>
-  </si>
-  <si>
-    <t>difference</t>
-  </si>
-  <si>
     <t>p1_</t>
   </si>
   <si>
@@ -174,10 +168,22 @@
     <t>Kr_ out</t>
   </si>
   <si>
-    <t>recovery_</t>
-  </si>
-  <si>
     <t>Kr_ in</t>
+  </si>
+  <si>
+    <t>Kr_ [%]</t>
+  </si>
+  <si>
+    <t>Kr2_ [%]</t>
+  </si>
+  <si>
+    <t>recovery in %</t>
+  </si>
+  <si>
+    <t>recovery_ in %</t>
+  </si>
+  <si>
+    <t>difference in %</t>
   </si>
 </sst>
 </file>
@@ -209,7 +215,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -228,24 +234,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FFA4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE400"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -260,17 +248,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -766,7 +750,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB47AB1A-2BFC-674F-8971-6B4457BC2F49}">
-  <dimension ref="A1:V50"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
@@ -813,11 +797,11 @@
         <v>1.79</v>
       </c>
       <c r="G2">
-        <f>C2+(D2-E2)*F2</f>
+        <f t="shared" ref="G2:G12" si="0">C2+(D2-E2)*F2</f>
         <v>1.2102657142857143</v>
       </c>
       <c r="H2">
-        <f>G2/B2</f>
+        <f t="shared" ref="H2:H12" si="1">G2/B2</f>
         <v>2.5213869047619046</v>
       </c>
     </row>
@@ -832,18 +816,18 @@
         <v>0.219</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E12" si="0">D3/7</f>
+        <f t="shared" ref="E3:E12" si="2">D3/7</f>
         <v>3.1285714285714285E-2</v>
       </c>
       <c r="F3">
         <v>20.48</v>
       </c>
       <c r="G3">
-        <f>C3+(D3-E3)*F3</f>
+        <f t="shared" si="0"/>
         <v>16.854388571428572</v>
       </c>
       <c r="H3">
-        <f>G3/B3</f>
+        <f t="shared" si="1"/>
         <v>16.687513437057991</v>
       </c>
     </row>
@@ -861,18 +845,18 @@
         <v>0.29599999999999999</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4.2285714285714281E-2</v>
       </c>
       <c r="F4">
         <v>3.5</v>
       </c>
       <c r="G4">
-        <f>C4+(D4-E4)*F4</f>
+        <f t="shared" si="0"/>
         <v>2.6779999999999999</v>
       </c>
       <c r="H4">
-        <f>G4/B4</f>
+        <f t="shared" si="1"/>
         <v>0.96678700361010828</v>
       </c>
     </row>
@@ -890,18 +874,18 @@
         <v>0.156</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.2285714285714287E-2</v>
       </c>
       <c r="F5">
         <v>5.3460000000000001</v>
       </c>
       <c r="G5">
-        <f>C5+(D5-E5)*F5</f>
+        <f t="shared" si="0"/>
         <v>4.1548365714285715</v>
       </c>
       <c r="H5">
-        <f>G5/B5</f>
+        <f t="shared" si="1"/>
         <v>0.87840096647538501</v>
       </c>
     </row>
@@ -919,18 +903,18 @@
         <v>0.27800000000000002</v>
       </c>
       <c r="E6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.9714285714285716E-2</v>
       </c>
       <c r="F6">
         <v>6.15</v>
       </c>
       <c r="G6">
-        <f>C6+(D6-E6)*F6</f>
+        <f t="shared" si="0"/>
         <v>4.8554571428571434</v>
       </c>
       <c r="H6">
-        <f>G6/B6</f>
+        <f t="shared" si="1"/>
         <v>0.87802118315680711</v>
       </c>
     </row>
@@ -948,18 +932,18 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="E7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4.8571428571428576E-3</v>
       </c>
       <c r="F7">
         <v>18.93</v>
       </c>
       <c r="G7">
-        <f>C7+(D7-E7)*F7</f>
+        <f t="shared" si="0"/>
         <v>14.091674285714285</v>
       </c>
       <c r="H7">
-        <f>G7/B7</f>
+        <f t="shared" si="1"/>
         <v>1.625337287856319</v>
       </c>
     </row>
@@ -977,18 +961,18 @@
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.3857142857142858E-2</v>
       </c>
       <c r="F8">
         <v>8.5500000000000007</v>
       </c>
       <c r="G8">
-        <f>C8+(D8-E8)*F8</f>
+        <f t="shared" si="0"/>
         <v>5.9308714285714288</v>
       </c>
       <c r="H8">
-        <f>G8/B8</f>
+        <f t="shared" si="1"/>
         <v>0.65102869687941045</v>
       </c>
     </row>
@@ -1006,18 +990,18 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.0714285714285714E-2</v>
       </c>
       <c r="F9">
         <v>11.43</v>
       </c>
       <c r="G9">
-        <f>C9+(D9-E9)*F9</f>
+        <f t="shared" si="0"/>
         <v>9.8747857142857143</v>
       </c>
       <c r="H9">
-        <f>G9/B9</f>
+        <f t="shared" si="1"/>
         <v>0.99947223828802767</v>
       </c>
     </row>
@@ -1035,18 +1019,18 @@
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="E10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="F10">
         <v>21.85</v>
       </c>
       <c r="G10">
-        <f>C10+(D10-E10)*F10</f>
+        <f t="shared" si="0"/>
         <v>16.9788</v>
       </c>
       <c r="H10">
-        <f>G10/B10</f>
+        <f t="shared" si="1"/>
         <v>1.0718939393939393</v>
       </c>
     </row>
@@ -1064,18 +1048,18 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="E11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>7.2857142857142851E-3</v>
       </c>
       <c r="F11">
         <v>22.6</v>
       </c>
       <c r="G11">
-        <f>C11+(D11-E11)*F11</f>
+        <f t="shared" si="0"/>
         <v>19.49794285714286</v>
       </c>
       <c r="H11">
-        <f>G11/B11</f>
+        <f t="shared" si="1"/>
         <v>0.96860123483074323</v>
       </c>
     </row>
@@ -1093,18 +1077,18 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="E12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="F12">
         <v>25.64</v>
       </c>
       <c r="G12">
-        <f>C12+(D12-E12)*F12</f>
+        <f t="shared" si="0"/>
         <v>22.35304</v>
       </c>
       <c r="H12">
-        <f>G12/B12</f>
+        <f t="shared" si="1"/>
         <v>1.0109923111714156</v>
       </c>
     </row>
@@ -1221,26 +1205,26 @@
         <v>0.44400000000000001</v>
       </c>
       <c r="I18">
-        <f t="shared" ref="I18:I27" si="1">H18/7</f>
+        <f t="shared" ref="I18:I27" si="3">H18/7</f>
         <v>6.3428571428571431E-2</v>
       </c>
       <c r="J18">
         <v>0.219</v>
       </c>
       <c r="K18">
-        <f t="shared" ref="K18:K27" si="2">J18/7</f>
+        <f t="shared" ref="K18:K27" si="4">J18/7</f>
         <v>3.1285714285714285E-2</v>
       </c>
       <c r="L18">
-        <f t="shared" ref="L18:L27" si="3">C18+D18*(H18-I18)*B18</f>
+        <f t="shared" ref="L18:L27" si="5">C18+D18*(H18-I18)*B18</f>
         <v>1.9416084114285712</v>
       </c>
       <c r="M18">
-        <f t="shared" ref="M18:M28" si="4">F18+G18*(J18-K18)*E18</f>
+        <f t="shared" ref="M18:M27" si="6">F18+G18*(J18-K18)*E18</f>
         <v>15.470408685714286</v>
       </c>
       <c r="N18">
-        <f t="shared" ref="N18:N27" si="5">M18/L18</f>
+        <f t="shared" ref="N18:N27" si="7">M18/L18</f>
         <v>7.9678315126023129</v>
       </c>
     </row>
@@ -1270,26 +1254,26 @@
         <v>0.16200000000000001</v>
       </c>
       <c r="I19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.3142857142857142E-2</v>
       </c>
       <c r="J19">
         <v>0.29599999999999999</v>
       </c>
       <c r="K19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.2285714285714281E-2</v>
       </c>
       <c r="L19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3.1553119085714285</v>
       </c>
       <c r="M19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.2437680000000002</v>
       </c>
       <c r="N19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.71110814557026436</v>
       </c>
     </row>
@@ -1319,26 +1303,26 @@
         <v>0.152</v>
       </c>
       <c r="I20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.1714285714285714E-2</v>
       </c>
       <c r="J20">
         <v>0.156</v>
       </c>
       <c r="K20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.2285714285714287E-2</v>
       </c>
       <c r="L20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.3461393828571433</v>
       </c>
       <c r="M20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.8996399154285712</v>
       </c>
       <c r="N20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.72943102230613421</v>
       </c>
     </row>
@@ -1368,26 +1352,26 @@
         <v>0.13600000000000001</v>
       </c>
       <c r="I21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.942857142857143E-2</v>
       </c>
       <c r="J21">
         <v>0.27800000000000002</v>
       </c>
       <c r="K21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.9714285714285716E-2</v>
       </c>
       <c r="L21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6.1754886400000002</v>
       </c>
       <c r="M21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4.1989323428571428</v>
       </c>
       <c r="N21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.67993523875337303</v>
       </c>
     </row>
@@ -1417,26 +1401,26 @@
         <v>0.34499999999999997</v>
       </c>
       <c r="I22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.928571428571428E-2</v>
       </c>
       <c r="J22">
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="K22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.8571428571428576E-3</v>
       </c>
       <c r="L22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>11.234463857142856</v>
       </c>
       <c r="M22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>13.934447114285714</v>
       </c>
       <c r="N22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1.2403304057475082</v>
       </c>
     </row>
@@ -1466,26 +1450,26 @@
         <v>0.11899999999999999</v>
       </c>
       <c r="I23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.6999999999999998E-2</v>
       </c>
       <c r="J23">
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="K23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3857142857142858E-2</v>
       </c>
       <c r="L23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>10.0391792</v>
       </c>
       <c r="M23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5.6543424428571427</v>
       </c>
       <c r="N23">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.56322756374915017</v>
       </c>
     </row>
@@ -1515,26 +1499,26 @@
         <v>0.112</v>
       </c>
       <c r="I24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.6E-2</v>
       </c>
       <c r="J24">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="K24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.0714285714285714E-2</v>
       </c>
       <c r="L24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>10.82845696</v>
       </c>
       <c r="M24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9.7270937857142865</v>
       </c>
       <c r="N24">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.89828992456135559</v>
       </c>
     </row>
@@ -1564,26 +1548,26 @@
         <v>0.34799999999999998</v>
       </c>
       <c r="I25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.9714285714285711E-2</v>
       </c>
       <c r="J25">
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="K25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="L25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20.566650342857145</v>
       </c>
       <c r="M25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>16.694575199999999</v>
       </c>
       <c r="N25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.81173039467742358</v>
       </c>
     </row>
@@ -1613,26 +1597,26 @@
         <v>3.9E-2</v>
       </c>
       <c r="I26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5.5714285714285718E-3</v>
       </c>
       <c r="J26">
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="K26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7.2857142857142851E-3</v>
       </c>
       <c r="L26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20.802897085714285</v>
       </c>
       <c r="M26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>19.319125200000002</v>
       </c>
       <c r="N26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.92867474757959478</v>
       </c>
     </row>
@@ -1662,90 +1646,92 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="I27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6.8571428571428577E-3</v>
       </c>
       <c r="J27">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="K27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="L27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>23.456538377142859</v>
       </c>
       <c r="M27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>22.201661439999999</v>
       </c>
       <c r="N27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.9465020406265201</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q33" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H33" s="6" t="s">
+      <c r="R33" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="M33" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N33" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="O33" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="P33" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="R33" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="U33" t="s">
-        <v>39</v>
-      </c>
-      <c r="V33" t="s">
-        <v>44</v>
-      </c>
+      <c r="S33" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="T33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B34">
@@ -1769,121 +1755,129 @@
         <v>1.64175</v>
       </c>
       <c r="H34">
-        <f>F34+G34*6/7*E34*D34</f>
-        <v>0.70640984464285717</v>
+        <f>D34/(1-6/7*E34)</f>
+        <v>0.54485488126649084</v>
       </c>
       <c r="I34">
+        <f>G34*H34</f>
+        <v>0.89451550131926139</v>
+      </c>
+      <c r="J34">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>1.5E-3</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>0.25800000000000001</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>0.48899999999999999</v>
       </c>
-      <c r="M34">
-        <f>(I34-J34)*K34*41.25</f>
+      <c r="N34">
+        <f>(J34-K34)*L34*41.25</f>
         <v>0.46294875000000002</v>
       </c>
-      <c r="N34">
-        <f>(I34-J34)*41.25</f>
+      <c r="O34">
+        <f>(J34-K34)*41.25</f>
         <v>1.7943749999999998</v>
       </c>
-      <c r="O34">
-        <f>M34+N34*6/7*L34*K34</f>
-        <v>0.65699041178571427</v>
-      </c>
       <c r="P34">
-        <f>M34/F34</f>
-        <v>0.95588110041734098</v>
+        <f>L34/(1-6/7*M34)</f>
+        <v>0.44417117560255776</v>
       </c>
       <c r="Q34">
-        <f>O34/H34</f>
-        <v>0.93004141543054497</v>
+        <f>P34*O34</f>
+        <v>0.79700965322183948</v>
       </c>
       <c r="R34">
-        <f>Q34-P34</f>
-        <v>-2.5839684986796008E-2</v>
-      </c>
-      <c r="U34">
-        <v>0.95588110041734098</v>
-      </c>
-      <c r="V34">
-        <v>0.93004141543054497</v>
-      </c>
+        <f>N34/F34*100</f>
+        <v>95.588110041734097</v>
+      </c>
+      <c r="S34">
+        <f>Q34/I34*100</f>
+        <v>89.099591012831297</v>
+      </c>
+      <c r="T34">
+        <f>S34-R34</f>
+        <v>-6.4885190289028003</v>
+      </c>
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2">
         <v>0.40200000000000002</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="2">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="2">
         <v>0.14799999999999999</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="2">
         <v>0.44400000000000001</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="2">
         <f>(B35-C35)*D35*17.09</f>
         <v>1.014004388</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G35" s="2">
         <f>(B35-C35)*17.09</f>
         <v>6.8513810000000008</v>
       </c>
-      <c r="H35" s="3">
-        <f>F35+G35*6/7*E35*D35</f>
-        <v>1.3999054865188572</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="H35" s="2">
+        <f t="shared" ref="H35:H44" si="8">D35/(1-6/7*E35)</f>
+        <v>0.23892988929889297</v>
+      </c>
+      <c r="I35" s="2">
+        <f t="shared" ref="I35:I44" si="9">G35*H35</f>
+        <v>1.6369997038745387</v>
+      </c>
+      <c r="J35" s="2">
         <v>0.4965</v>
       </c>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3">
+      <c r="K35" s="2"/>
+      <c r="L35" s="2">
         <v>0.64</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="2">
         <v>0.219</v>
       </c>
-      <c r="M35" s="3">
-        <f t="shared" ref="M35:M44" si="6">(I35-J35)*K35*41.25</f>
+      <c r="N35" s="2">
+        <f t="shared" ref="N35:N44" si="10">(J35-K35)*L35*41.25</f>
         <v>13.1076</v>
       </c>
-      <c r="N35" s="3">
-        <f>(I35-J35)*41.25</f>
+      <c r="O35" s="2">
+        <f>(J35-K35)*41.25</f>
         <v>20.480625</v>
       </c>
-      <c r="O35" s="3">
-        <f>M35+N35*6/7*L35*K35</f>
-        <v>15.56808377142857</v>
-      </c>
-      <c r="P35" s="3">
-        <f>M35/F35</f>
-        <v>12.926571280281284</v>
-      </c>
-      <c r="Q35" s="3">
-        <f>O35/H35</f>
-        <v>11.120810598536691</v>
-      </c>
-      <c r="R35" s="3">
-        <f t="shared" ref="R35:R44" si="7">Q35-P35</f>
-        <v>-1.8057606817445926</v>
-      </c>
-      <c r="U35">
-        <v>12.926571280281284</v>
-      </c>
-      <c r="V35">
-        <v>11.120810598536691</v>
-      </c>
+      <c r="P35" s="2">
+        <f t="shared" ref="P35:P44" si="11">L35/(1-6/7*M35)</f>
+        <v>0.78790010552233558</v>
+      </c>
+      <c r="Q35" s="2">
+        <f t="shared" ref="Q35:Q44" si="12">P35*O35</f>
+        <v>16.136686598663385</v>
+      </c>
+      <c r="R35" s="2">
+        <f t="shared" ref="R35:R44" si="13">N35/F35*100</f>
+        <v>1292.6571280281285</v>
+      </c>
+      <c r="S35" s="2">
+        <f t="shared" ref="S35:S44" si="14">Q35/I35*100</f>
+        <v>985.74767976256862</v>
+      </c>
+      <c r="T35" s="2">
+        <f t="shared" ref="T35:T44" si="15">S35-R35</f>
+        <v>-306.90944826555983</v>
+      </c>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B36">
@@ -1899,62 +1893,66 @@
         <v>0.16200000000000001</v>
       </c>
       <c r="F36">
-        <f t="shared" ref="F35:F44" si="8">(B36-C36)*D36*41.25</f>
+        <f t="shared" ref="F36:F44" si="16">(B36-C36)*D36*41.25</f>
         <v>2.7762899999999999</v>
       </c>
       <c r="G36">
-        <f t="shared" ref="G35:G44" si="9">(B36-C36)*41.25</f>
+        <f t="shared" ref="G36:G44" si="17">(B36-C36)*41.25</f>
         <v>3.691875</v>
       </c>
       <c r="H36">
-        <f t="shared" ref="H35:H59" si="10">F36+G36*6/7*E36*D36</f>
-        <v>3.1617976971428572</v>
+        <f t="shared" si="8"/>
+        <v>0.87325812873258124</v>
       </c>
       <c r="I36">
+        <f t="shared" si="9"/>
+        <v>3.2239598540145984</v>
+      </c>
+      <c r="J36">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>1E-3</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>0.51100000000000001</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>0.29599999999999999</v>
       </c>
-      <c r="M36">
-        <f t="shared" si="6"/>
+      <c r="N36">
+        <f t="shared" si="10"/>
         <v>1.7916937499999999</v>
       </c>
-      <c r="N36">
-        <f t="shared" ref="N35:N44" si="11">(I36-J36)*41.25</f>
+      <c r="O36">
+        <f t="shared" ref="O36:O44" si="18">(J36-K36)*41.25</f>
         <v>3.5062499999999996</v>
       </c>
-      <c r="O36">
-        <f>M36+N36*6/7*L36*K36</f>
-        <v>2.24627205</v>
-      </c>
       <c r="P36">
-        <f>M36/F36</f>
-        <v>0.64535540235350053</v>
+        <f t="shared" si="11"/>
+        <v>0.6847243491577335</v>
       </c>
       <c r="Q36">
-        <f>O36/H36</f>
-        <v>0.71044142135653798</v>
+        <f t="shared" si="12"/>
+        <v>2.400814749234303</v>
       </c>
       <c r="R36">
-        <f t="shared" si="7"/>
-        <v>6.5086019003037454E-2</v>
-      </c>
-      <c r="U36">
-        <v>0.64535540235350053</v>
-      </c>
-      <c r="V36">
-        <v>0.71044142135653798</v>
-      </c>
+        <f t="shared" si="13"/>
+        <v>64.535540235350055</v>
+      </c>
+      <c r="S36">
+        <f t="shared" si="14"/>
+        <v>74.467886014297491</v>
+      </c>
+      <c r="T36">
+        <f t="shared" si="15"/>
+        <v>9.9323457789474361</v>
+      </c>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B37">
@@ -1970,62 +1968,66 @@
         <v>0.152</v>
       </c>
       <c r="F37">
+        <f t="shared" si="16"/>
+        <v>4.7252700000000001</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="17"/>
+        <v>6.1049999999999995</v>
+      </c>
+      <c r="H37">
         <f t="shared" si="8"/>
-        <v>4.7252700000000001</v>
-      </c>
-      <c r="G37">
+        <v>0.88994743758212891</v>
+      </c>
+      <c r="I37">
         <f t="shared" si="9"/>
-        <v>6.1049999999999995</v>
-      </c>
-      <c r="H37">
+        <v>5.4331291064388969</v>
+      </c>
+      <c r="J37">
+        <v>0.1308</v>
+      </c>
+      <c r="K37">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="L37">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="M37">
+        <v>0.156</v>
+      </c>
+      <c r="N37">
         <f t="shared" si="10"/>
-        <v>5.3409051771428571</v>
-      </c>
-      <c r="I37">
-        <v>0.1308</v>
-      </c>
-      <c r="J37">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="K37">
-        <v>0.64300000000000002</v>
-      </c>
-      <c r="L37">
-        <v>0.156</v>
-      </c>
-      <c r="M37">
-        <f t="shared" si="6"/>
         <v>3.437478</v>
       </c>
-      <c r="N37">
+      <c r="O37">
+        <f t="shared" si="18"/>
+        <v>5.3460000000000001</v>
+      </c>
+      <c r="P37">
         <f t="shared" si="11"/>
-        <v>5.3460000000000001</v>
-      </c>
-      <c r="O37">
-        <f>M37+N37*6/7*L37*K37</f>
-        <v>3.8971179154285713</v>
-      </c>
-      <c r="P37">
-        <f>M37/F37</f>
-        <v>0.72746700188560653</v>
+        <v>0.74224934036939316</v>
       </c>
       <c r="Q37">
-        <f>O37/H37</f>
-        <v>0.72967367630993096</v>
+        <f t="shared" si="12"/>
+        <v>3.9680649736147759</v>
       </c>
       <c r="R37">
-        <f t="shared" si="7"/>
-        <v>2.2066744243244285E-3</v>
-      </c>
-      <c r="U37">
-        <v>0.72746700188560653</v>
-      </c>
-      <c r="V37">
-        <v>0.72967367630993096</v>
-      </c>
+        <f t="shared" si="13"/>
+        <v>72.746700188560652</v>
+      </c>
+      <c r="S37">
+        <f t="shared" si="14"/>
+        <v>73.034615888515376</v>
+      </c>
+      <c r="T37">
+        <f t="shared" si="15"/>
+        <v>0.28791569995472344</v>
+      </c>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B38">
@@ -2041,62 +2043,66 @@
         <v>0.13600000000000001</v>
       </c>
       <c r="F38">
+        <f t="shared" si="16"/>
+        <v>5.5335719999999995</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="17"/>
+        <v>6.7154999999999996</v>
+      </c>
+      <c r="H38">
         <f t="shared" si="8"/>
-        <v>5.5335719999999995</v>
-      </c>
-      <c r="G38">
+        <v>0.93272962483829225</v>
+      </c>
+      <c r="I38">
         <f t="shared" si="9"/>
-        <v>6.7154999999999996</v>
-      </c>
-      <c r="H38">
+        <v>6.263745795601551</v>
+      </c>
+      <c r="J38">
+        <v>0.15</v>
+      </c>
+      <c r="K38">
+        <v>1E-3</v>
+      </c>
+      <c r="L38">
+        <v>0.55200000000000005</v>
+      </c>
+      <c r="M38">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="N38">
         <f t="shared" si="10"/>
-        <v>6.1786283931428567</v>
-      </c>
-      <c r="I38">
-        <v>0.15</v>
-      </c>
-      <c r="J38">
-        <v>1E-3</v>
-      </c>
-      <c r="K38">
-        <v>0.55200000000000005</v>
-      </c>
-      <c r="L38">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="M38" s="2">
-        <f t="shared" si="6"/>
         <v>3.3927300000000002</v>
       </c>
-      <c r="N38">
+      <c r="O38">
+        <f t="shared" si="18"/>
+        <v>6.1462499999999993</v>
+      </c>
+      <c r="P38">
         <f t="shared" si="11"/>
-        <v>6.1462499999999993</v>
-      </c>
-      <c r="O38">
-        <f>M38+N38*6/7*L38*K38</f>
-        <v>4.2011690914285715</v>
-      </c>
-      <c r="P38">
-        <f>M38/F38</f>
-        <v>0.6131175305932588</v>
+        <v>0.72468117029257328</v>
       </c>
       <c r="Q38">
-        <f>O38/H38</f>
-        <v>0.67995173428638267</v>
+        <f t="shared" si="12"/>
+        <v>4.4540716429107281</v>
       </c>
       <c r="R38">
-        <f t="shared" si="7"/>
-        <v>6.6834203693123873E-2</v>
-      </c>
-      <c r="U38">
-        <v>0.6131175305932588</v>
-      </c>
-      <c r="V38">
-        <v>0.67995173428638267</v>
-      </c>
+        <f t="shared" si="13"/>
+        <v>61.311753059325881</v>
+      </c>
+      <c r="S38">
+        <f t="shared" si="14"/>
+        <v>71.108754861003618</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="15"/>
+        <v>9.7970018016777374</v>
+      </c>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B39">
@@ -2108,63 +2114,67 @@
       <c r="E39">
         <v>0.34499999999999997</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39">
+        <f t="shared" si="16"/>
+        <v>8.6972737500000008</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="17"/>
+        <v>21.161249999999999</v>
+      </c>
+      <c r="H39">
         <f t="shared" si="8"/>
-        <v>8.6972737500000008</v>
-      </c>
-      <c r="G39">
+        <v>0.5835699797160242</v>
+      </c>
+      <c r="I39">
         <f t="shared" si="9"/>
-        <v>21.161249999999999</v>
-      </c>
-      <c r="H39">
-        <f t="shared" si="10"/>
-        <v>11.269181844642858</v>
-      </c>
-      <c r="I39">
+        <v>12.349070233265717</v>
+      </c>
+      <c r="J39">
         <v>0.46050000000000002</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>1.5E-3</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>0.71499999999999997</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="M39">
-        <f t="shared" si="6"/>
+      <c r="N39">
+        <f>(J39-K39)*L39*41.25</f>
         <v>13.53763125</v>
       </c>
-      <c r="N39">
+      <c r="O39">
+        <f t="shared" si="18"/>
+        <v>18.93375</v>
+      </c>
+      <c r="P39">
         <f t="shared" si="11"/>
-        <v>18.93375</v>
-      </c>
-      <c r="O39">
-        <f>M39+N39*6/7*L39*K39</f>
-        <v>13.932156503571429</v>
-      </c>
-      <c r="P39">
-        <f>M39/F39</f>
-        <v>1.556537328723268</v>
+        <v>0.73646262507357263</v>
       </c>
       <c r="Q39">
-        <f>O39/H39</f>
-        <v>1.2363059444456914</v>
+        <f t="shared" si="12"/>
+        <v>13.943999227486756</v>
       </c>
       <c r="R39">
-        <f t="shared" si="7"/>
-        <v>-0.32023138427757658</v>
-      </c>
-      <c r="U39">
-        <v>1.556537328723268</v>
-      </c>
-      <c r="V39">
-        <v>1.2363059444456914</v>
-      </c>
+        <f t="shared" si="13"/>
+        <v>155.6537328723268</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="14"/>
+        <v>112.91537714252078</v>
+      </c>
+      <c r="T39">
+        <f t="shared" si="15"/>
+        <v>-42.738355729806017</v>
+      </c>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B40">
@@ -2180,62 +2190,66 @@
         <v>0.11899999999999999</v>
       </c>
       <c r="F40">
+        <f t="shared" si="16"/>
+        <v>9.1076699999999988</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="17"/>
+        <v>11.797499999999999</v>
+      </c>
+      <c r="H40">
         <f t="shared" si="8"/>
-        <v>9.1076699999999988</v>
-      </c>
-      <c r="G40">
+        <v>0.85968819599109136</v>
+      </c>
+      <c r="I40">
         <f t="shared" si="9"/>
-        <v>11.797499999999999</v>
-      </c>
-      <c r="H40">
-        <f t="shared" si="10"/>
-        <v>10.036652339999998</v>
-      </c>
-      <c r="I40">
+        <v>10.1421714922049</v>
+      </c>
+      <c r="J40">
         <v>0.20899999999999999</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>0.61099999999999999</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="M40">
-        <f t="shared" si="6"/>
+      <c r="N40">
+        <f t="shared" ref="N40:N44" si="19">(J40-K40)*L40*41.25</f>
         <v>5.2247373749999992</v>
       </c>
-      <c r="N40">
+      <c r="O40">
+        <f t="shared" si="18"/>
+        <v>8.551124999999999</v>
+      </c>
+      <c r="P40">
         <f t="shared" si="11"/>
-        <v>8.551124999999999</v>
-      </c>
-      <c r="O40">
-        <f>M40+N40*6/7*L40*K40</f>
-        <v>5.6591369681785704</v>
-      </c>
-      <c r="P40">
-        <f>M40/F40</f>
-        <v>0.57366344795101276</v>
+        <v>0.66640698036771584</v>
       </c>
       <c r="Q40">
-        <f>O40/H40</f>
-        <v>0.5638470653830151</v>
+        <f t="shared" si="12"/>
+        <v>5.6985293899968834</v>
       </c>
       <c r="R40">
-        <f t="shared" si="7"/>
-        <v>-9.8163825679976613E-3</v>
-      </c>
-      <c r="U40">
-        <v>0.57366344795101276</v>
-      </c>
-      <c r="V40" s="8">
-        <v>0.5638470653830151</v>
-      </c>
+        <f t="shared" si="13"/>
+        <v>57.366344795101277</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="14"/>
+        <v>56.186482296978269</v>
+      </c>
+      <c r="T40">
+        <f t="shared" si="15"/>
+        <v>-1.1798624981230077</v>
+      </c>
+      <c r="U40" s="5"/>
+      <c r="V40" s="5"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B41">
@@ -2251,62 +2265,66 @@
         <v>0.112</v>
       </c>
       <c r="F41">
+        <f t="shared" si="16"/>
+        <v>9.8808929999999986</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="17"/>
+        <v>11.991374999999998</v>
+      </c>
+      <c r="H41">
         <f t="shared" si="8"/>
-        <v>9.8808929999999986</v>
-      </c>
-      <c r="G41">
+        <v>0.91150442477876104</v>
+      </c>
+      <c r="I41">
         <f t="shared" si="9"/>
-        <v>11.991374999999998</v>
-      </c>
-      <c r="H41">
-        <f t="shared" si="10"/>
-        <v>10.829458727999999</v>
-      </c>
-      <c r="I41">
+        <v>10.930191371681413</v>
+      </c>
+      <c r="J41">
         <v>0.27900000000000003</v>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>0.79900000000000004</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="M41">
-        <f t="shared" si="6"/>
+      <c r="N41">
+        <f t="shared" si="19"/>
         <v>9.1394613750000016</v>
       </c>
-      <c r="N41">
+      <c r="O41">
+        <f t="shared" si="18"/>
+        <v>11.438625000000002</v>
+      </c>
+      <c r="P41">
         <f t="shared" si="11"/>
-        <v>11.438625000000002</v>
-      </c>
-      <c r="O41">
-        <f>M41+N41*6/7*L41*K41</f>
-        <v>9.7269981776785723</v>
-      </c>
-      <c r="P41">
-        <f>M41/F41</f>
-        <v>0.92496309544086786</v>
+        <v>0.85389312977099241</v>
       </c>
       <c r="Q41">
-        <f>O41/H41</f>
-        <v>0.8981980006562128</v>
+        <f t="shared" si="12"/>
+        <v>9.7673633015267196</v>
       </c>
       <c r="R41">
-        <f t="shared" si="7"/>
-        <v>-2.6765094784655052E-2</v>
-      </c>
-      <c r="U41">
-        <v>0.92496309544086786</v>
-      </c>
-      <c r="V41" s="7">
-        <v>0.8981980006562128</v>
-      </c>
+        <f t="shared" si="13"/>
+        <v>92.496309544086785</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="14"/>
+        <v>89.361320121371179</v>
+      </c>
+      <c r="T41">
+        <f t="shared" si="15"/>
+        <v>-3.1349894227156057</v>
+      </c>
+      <c r="U41" s="5"/>
+      <c r="V41" s="5"/>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B42">
@@ -2322,62 +2340,66 @@
         <v>0.34799999999999998</v>
       </c>
       <c r="F42">
+        <f t="shared" si="16"/>
+        <v>15.845403749999999</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="17"/>
+        <v>30.64875</v>
+      </c>
+      <c r="H42">
         <f t="shared" si="8"/>
-        <v>15.845403749999999</v>
-      </c>
-      <c r="G42">
+        <v>0.73676710097719866</v>
+      </c>
+      <c r="I42">
         <f t="shared" si="9"/>
-        <v>30.64875</v>
-      </c>
-      <c r="H42">
-        <f t="shared" si="10"/>
-        <v>20.571861325714284</v>
-      </c>
-      <c r="I42">
+        <v>22.580990686074916</v>
+      </c>
+      <c r="J42">
         <v>0.53090000000000004</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="K42">
+      <c r="L42">
         <v>0.72899999999999998</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="M42">
-        <f t="shared" si="6"/>
+      <c r="N42">
+        <f t="shared" si="19"/>
         <v>15.93174825</v>
       </c>
-      <c r="N42">
+      <c r="O42">
+        <f t="shared" si="18"/>
+        <v>21.85425</v>
+      </c>
+      <c r="P42">
         <f t="shared" si="11"/>
-        <v>21.85425</v>
-      </c>
-      <c r="O42">
-        <f>M42+N42*6/7*L42*K42</f>
-        <v>16.696472166</v>
-      </c>
-      <c r="P42">
-        <f>M42/F42</f>
-        <v>1.0054491827006933</v>
+        <v>0.76575630252100846</v>
       </c>
       <c r="Q42">
-        <f>O42/H42</f>
-        <v>0.81161698990892228</v>
+        <f t="shared" si="12"/>
+        <v>16.735029674369748</v>
       </c>
       <c r="R42">
-        <f t="shared" si="7"/>
-        <v>-0.193832192791771</v>
-      </c>
-      <c r="U42">
-        <v>1.0054491827006933</v>
-      </c>
-      <c r="V42" s="9">
-        <v>0.81161698990892228</v>
-      </c>
+        <f t="shared" si="13"/>
+        <v>100.54491827006933</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="14"/>
+        <v>74.11114023748209</v>
+      </c>
+      <c r="T42">
+        <f t="shared" si="15"/>
+        <v>-26.433778032587242</v>
+      </c>
+      <c r="U42" s="5"/>
+      <c r="V42" s="5"/>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B43">
@@ -2393,62 +2415,66 @@
         <v>3.9E-2</v>
       </c>
       <c r="F43">
+        <f t="shared" si="16"/>
+        <v>20.131773750000001</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="17"/>
+        <v>31.803750000000001</v>
+      </c>
+      <c r="H43">
         <f t="shared" si="8"/>
-        <v>20.131773750000001</v>
-      </c>
-      <c r="G43">
+        <v>0.6548921075968076</v>
+      </c>
+      <c r="I43">
         <f t="shared" si="9"/>
-        <v>31.803750000000001</v>
-      </c>
-      <c r="H43">
-        <f t="shared" si="10"/>
-        <v>20.804750186785714</v>
-      </c>
-      <c r="I43">
+        <v>20.82802486698197</v>
+      </c>
+      <c r="J43">
         <v>0.54900000000000004</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>0.81899999999999995</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="M43">
-        <f t="shared" si="6"/>
+      <c r="N43">
+        <f t="shared" si="19"/>
         <v>18.506738250000001</v>
       </c>
-      <c r="N43">
+      <c r="O43">
+        <f t="shared" si="18"/>
+        <v>22.596750000000004</v>
+      </c>
+      <c r="P43">
         <f t="shared" si="11"/>
-        <v>22.596750000000004</v>
-      </c>
-      <c r="O43">
-        <f>M43+N43*6/7*L43*K43</f>
-        <v>19.315747093500001</v>
-      </c>
-      <c r="P43">
-        <f>M43/F43</f>
-        <v>0.91928006343703328</v>
+        <v>0.8564386017328951</v>
       </c>
       <c r="Q43">
-        <f>O43/H43</f>
-        <v>0.92842965765426666</v>
+        <f t="shared" si="12"/>
+        <v>19.352728973707801</v>
       </c>
       <c r="R43">
-        <f t="shared" si="7"/>
-        <v>9.1495942172333811E-3</v>
-      </c>
-      <c r="U43">
-        <v>0.91928006343703328</v>
-      </c>
-      <c r="V43">
-        <v>0.92842965765426666</v>
-      </c>
+        <f t="shared" si="13"/>
+        <v>91.928006343703331</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="14"/>
+        <v>92.916774861293206</v>
+      </c>
+      <c r="T43">
+        <f t="shared" si="15"/>
+        <v>0.98876851758987527</v>
+      </c>
+      <c r="U43" s="5"/>
+      <c r="V43" s="5"/>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B44">
@@ -2464,62 +2490,67 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="F44">
+        <f t="shared" si="16"/>
+        <v>22.527829499999999</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="17"/>
+        <v>27.439499999999999</v>
+      </c>
+      <c r="H44">
         <f t="shared" si="8"/>
-        <v>22.527829499999999</v>
-      </c>
-      <c r="G44">
+        <v>0.85622765196662687</v>
+      </c>
+      <c r="I44">
         <f t="shared" si="9"/>
-        <v>27.439499999999999</v>
-      </c>
-      <c r="H44">
-        <f t="shared" si="10"/>
-        <v>23.454688770857143</v>
-      </c>
-      <c r="I44">
+        <v>23.494458656138256</v>
+      </c>
+      <c r="J44">
         <v>0.62270000000000003</v>
       </c>
-      <c r="J44">
+      <c r="K44">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="K44">
+      <c r="L44">
         <v>0.83599999999999997</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="M44">
-        <f t="shared" si="6"/>
+      <c r="N44">
+        <f t="shared" si="19"/>
         <v>21.432427499999999</v>
       </c>
-      <c r="N44">
+      <c r="O44">
+        <f t="shared" si="18"/>
+        <v>25.636875000000003</v>
+      </c>
+      <c r="P44">
         <f t="shared" si="11"/>
-        <v>25.636875000000003</v>
-      </c>
-      <c r="O44">
-        <f>M44+N44*6/7*L44*K44</f>
-        <v>22.203994890000001</v>
-      </c>
-      <c r="P44">
-        <f>M44/F44</f>
-        <v>0.95137560855563119</v>
+        <v>0.86721991701244816</v>
       </c>
       <c r="Q44">
-        <f>O44/H44</f>
-        <v>0.94667616811819943</v>
+        <f t="shared" si="12"/>
+        <v>22.232808609958511</v>
       </c>
       <c r="R44">
-        <f t="shared" si="7"/>
-        <v>-4.6994404374317567E-3</v>
-      </c>
-      <c r="U44">
-        <v>0.95137560855563119</v>
-      </c>
-      <c r="V44" s="8">
-        <v>0.94667616811819943</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" s="2"/>
+        <f t="shared" si="13"/>
+        <v>95.137560855563123</v>
+      </c>
+      <c r="S44">
+        <f t="shared" si="14"/>
+        <v>94.630010145604601</v>
+      </c>
+      <c r="T44">
+        <f t="shared" si="15"/>
+        <v>-0.50755070995852236</v>
+      </c>
+      <c r="U44" s="5"/>
+      <c r="V44" s="5"/>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="U45" s="5"/>
+      <c r="V45" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Kr-Ar Separation/analysis/2026_08_recovery_for_different_amounts/volume_v_recovery.xlsx
+++ b/Kr-Ar Separation/analysis/2026_08_recovery_for_different_amounts/volume_v_recovery.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fatmayakut/Desktop/Physik/MA/Kr-Ar Separation/analysis/2026_08_recovery_for_different_amounts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0D8060-DB6E-1849-98FF-660A5AFCF403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FF981F-1631-4545-A830-B2E8ABC3F82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="980" yWindow="600" windowWidth="23280" windowHeight="17400" activeTab="1" xr2:uid="{8B558523-AAC9-124C-AA38-7CB1369EC6B4}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{8B558523-AAC9-124C-AA38-7CB1369EC6B4}"/>
   </bookViews>
   <sheets>
     <sheet name="volume_v_recovery" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
   <si>
     <t>Recovery</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>difference in %</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -750,7 +753,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB47AB1A-2BFC-674F-8971-6B4457BC2F49}">
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
@@ -2159,7 +2162,7 @@
         <v>13.943999227486756</v>
       </c>
       <c r="R39">
-        <f t="shared" si="13"/>
+        <f>N39/F39*100</f>
         <v>155.6537328723268</v>
       </c>
       <c r="S39">
@@ -2551,6 +2554,11 @@
     <row r="45" spans="1:22" x14ac:dyDescent="0.2">
       <c r="U45" s="5"/>
       <c r="V45" s="5"/>
+    </row>
+    <row r="56" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I56" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
